--- a/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Triphammer_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Chobani - Peach</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15.39</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Chobani - Vanilla</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>30.78</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30.78</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Naked - Berry Blast</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>48.48</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Naked - Green Machine</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24.24</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Naked - Mighty Mango</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48.48</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>PKT Ketchup</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="E7" t="n">
+        <v>39.43</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Gatorade Lemon Lime</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>29.40</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>29.40</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>29.4</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Cakerie - Cake Chocolate Dreamin' GF</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>80.99</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>80.99</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>80.98999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Frz Lemonade</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>47.50</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>47.50</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>47.5</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,6 +632,636 @@
         <v>47.5</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7613284</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Can - Coconut Milk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="E11" t="n">
+        <v>111.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4032991</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Corn Starch</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6889125</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cranberries - Sweet Dried (sliced)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31.96</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4617771</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Egg Patty</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>706.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7456025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Egg White Patty</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="E15" t="n">
+        <v>139.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0017354</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hash Brown</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="E16" t="n">
+        <v>143.34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1589290</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sausage - Patty (1.5oz)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E17" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7081642</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Vinegar - Red Raspberry</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="E18" t="n">
+        <v>32.55</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1956804</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Asiago (Shredded)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E19" t="n">
+        <v>57.85</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2536555</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bacon (Pre-Cooked)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1042.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2916427</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Base - Chicken (No MSG)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>186.36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0566824</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Beef - Ground</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>146.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7256054</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cheddar - Orange (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>38</v>
+      </c>
+      <c r="E23" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>7133036</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Chicken - Diced White &amp; Dark</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="E24" t="n">
+        <v>439.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4438911</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Grain Blend 5 Way</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>77.89</v>
+      </c>
+      <c r="E25" t="n">
+        <v>233.67</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4828802</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Heavy Cream</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>89.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7524051</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hot Sauce - Franks Gal</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="E27" t="n">
+        <v>56.91</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4171902</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Manchego Cheese</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>84.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4579587</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="E29" t="n">
+        <v>365.76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3157690</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rice - Jasmine</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="E30" t="n">
+        <v>35.84</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3617531</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Roasted Root Vegetables</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="E31" t="n">
+        <v>116.98</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8489148</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Smoked Turkey (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="E32" t="n">
+        <v>614.88</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7820321</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tortellini - Cheese</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E33" t="n">
+        <v>187.96</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7108577</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tortilla Strips - Bulk</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="E34" t="n">
+        <v>43.75</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7161191</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Vegan Mozz</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>82.48999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3335504</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Wrap - White Flour (10")</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="E36" t="n">
+        <v>37.55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1735372</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cucumber (English)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E37" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8367371</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Butternut Squash - Fresh (prepped)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="E38" t="n">
+        <v>60.45</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0683696</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tomato - Fresh Sliced</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="E39" t="n">
+        <v>321.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0527952</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Herb - Fennel (Fresh)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="E40" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
